--- a/mi_cartera_balanz/data/ordenes.xlsx
+++ b/mi_cartera_balanz/data/ordenes.xlsx
@@ -610,7 +610,7 @@
         <v>Rescate a Cuenta Balanz</v>
       </c>
       <c r="B7" t="str">
-        <v>En Ejecución</v>
+        <v>Ejecutada</v>
       </c>
       <c r="C7">
         <v>108106197</v>
